--- a/artfynd/A 31420-2026 artfynd.xlsx
+++ b/artfynd/A 31420-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420187</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136420328</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>136419656</v>
       </c>
       <c r="B16" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>136420241</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136420287</v>
       </c>
       <c r="B18" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136419924</v>
       </c>
       <c r="B19" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31420-2026 artfynd.xlsx
+++ b/artfynd/A 31420-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420187</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136420328</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136419946</v>
       </c>
       <c r="B4" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136419683</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136419698</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136419778</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136419835</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136419889</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136420082</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136420138</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136420155</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136420206</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136419852</v>
       </c>
       <c r="B14" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136420118</v>
       </c>
       <c r="B15" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>136419656</v>
       </c>
       <c r="B16" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>136420241</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136420287</v>
       </c>
       <c r="B18" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136419924</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 31420-2026 artfynd.xlsx
+++ b/artfynd/A 31420-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136420187</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136420328</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136419946</v>
       </c>
       <c r="B4" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136419683</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136419698</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136419778</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>136419835</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136419889</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136420082</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136420138</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>136420155</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>136420206</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>136419852</v>
       </c>
       <c r="B14" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>136419656</v>
       </c>
       <c r="B16" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>136420241</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136420287</v>
       </c>
       <c r="B18" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136419924</v>
       </c>
       <c r="B19" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
